--- a/research/traditional_assets/database/data/romania/romania_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_financial_svcs_non_bank_insurance.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0638</v>
+        <v>0.0843</v>
       </c>
       <c r="E2">
-        <v>-0.119</v>
+        <v>0.0407</v>
       </c>
       <c r="G2">
-        <v>0.2178217821782178</v>
+        <v>0.1261261261261261</v>
       </c>
       <c r="H2">
-        <v>0.2178217821782178</v>
+        <v>0.1261261261261261</v>
       </c>
       <c r="I2">
-        <v>0.007821782178217822</v>
+        <v>0.1927927927927928</v>
       </c>
       <c r="J2">
-        <v>0.006626426762277557</v>
+        <v>0.165241198645454</v>
       </c>
       <c r="K2">
-        <v>0.848</v>
+        <v>2.45</v>
       </c>
       <c r="L2">
-        <v>0.08396039603960397</v>
+        <v>0.2207207207207207</v>
       </c>
       <c r="M2">
-        <v>2.01</v>
+        <v>1.743</v>
       </c>
       <c r="N2">
-        <v>0.04285714285714285</v>
+        <v>0.02852700490998364</v>
       </c>
       <c r="O2">
-        <v>2.370283018867924</v>
+        <v>0.7114285714285714</v>
       </c>
       <c r="P2">
-        <v>2.01</v>
+        <v>1.53</v>
       </c>
       <c r="Q2">
-        <v>0.04285714285714285</v>
+        <v>0.02504091653027823</v>
       </c>
       <c r="R2">
-        <v>2.370283018867924</v>
+        <v>0.6244897959183673</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.2130000000000001</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1222030981067126</v>
       </c>
       <c r="U2">
-        <v>3.16</v>
+        <v>2.22</v>
       </c>
       <c r="V2">
-        <v>0.06737739872068231</v>
+        <v>0.03633387888707038</v>
       </c>
       <c r="W2">
-        <v>0.03261538461538462</v>
+        <v>0.1004098360655738</v>
       </c>
       <c r="X2">
-        <v>0.02757358565869102</v>
+        <v>0.05436035006801698</v>
       </c>
       <c r="Y2">
-        <v>0.005041798956693599</v>
+        <v>0.0460494859975568</v>
       </c>
       <c r="Z2">
-        <v>0.42878369772872</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="AA2">
-        <v>0.002841303769857921</v>
+        <v>0.07995541869941322</v>
       </c>
       <c r="AB2">
-        <v>0.02784538127976801</v>
+        <v>0.05450490775238739</v>
       </c>
       <c r="AC2">
-        <v>-0.02500407750991009</v>
+        <v>0.02545051094702584</v>
       </c>
       <c r="AD2">
-        <v>1.7</v>
+        <v>1.13</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.7</v>
+        <v>1.13</v>
       </c>
       <c r="AG2">
-        <v>-1.46</v>
+        <v>-1.09</v>
       </c>
       <c r="AH2">
-        <v>0.03497942386831276</v>
+        <v>0.01815844448015426</v>
       </c>
       <c r="AI2">
-        <v>0.04815864022662888</v>
+        <v>0.03725684141114408</v>
       </c>
       <c r="AJ2">
-        <v>-0.03213028169014085</v>
+        <v>-0.01816363939343443</v>
       </c>
       <c r="AK2">
-        <v>-0.04542626011200996</v>
+        <v>-0.03877623621487016</v>
       </c>
       <c r="AL2">
-        <v>0.07099999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="AM2">
-        <v>-0.5760000000000001</v>
+        <v>-0.569</v>
       </c>
       <c r="AN2">
-        <v>2.230971128608924</v>
+        <v>0.4094202898550725</v>
       </c>
       <c r="AO2">
-        <v>1.112676056338028</v>
+        <v>32.42424242424242</v>
       </c>
       <c r="AP2">
-        <v>-1.916010498687664</v>
+        <v>-0.3949275362318842</v>
       </c>
       <c r="AQ2">
-        <v>-0.1371527777777778</v>
+        <v>-3.760984182776802</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0638</v>
+        <v>0.0843</v>
       </c>
       <c r="E3">
-        <v>-0.119</v>
+        <v>0.0407</v>
       </c>
       <c r="G3">
-        <v>0.2178217821782178</v>
+        <v>0.1261261261261261</v>
       </c>
       <c r="H3">
-        <v>0.2178217821782178</v>
+        <v>0.1261261261261261</v>
       </c>
       <c r="I3">
-        <v>0.007821782178217822</v>
+        <v>0.1927927927927928</v>
       </c>
       <c r="J3">
-        <v>0.006626426762277557</v>
+        <v>0.165241198645454</v>
       </c>
       <c r="K3">
-        <v>0.848</v>
+        <v>2.45</v>
       </c>
       <c r="L3">
-        <v>0.08396039603960397</v>
+        <v>0.2207207207207207</v>
       </c>
       <c r="M3">
-        <v>2.01</v>
+        <v>1.743</v>
       </c>
       <c r="N3">
-        <v>0.04285714285714285</v>
+        <v>0.02852700490998364</v>
       </c>
       <c r="O3">
-        <v>2.370283018867924</v>
+        <v>0.7114285714285714</v>
       </c>
       <c r="P3">
-        <v>2.01</v>
+        <v>1.53</v>
       </c>
       <c r="Q3">
-        <v>0.04285714285714285</v>
+        <v>0.02504091653027823</v>
       </c>
       <c r="R3">
-        <v>2.370283018867924</v>
+        <v>0.6244897959183673</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.2130000000000001</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.1222030981067126</v>
       </c>
       <c r="U3">
-        <v>3.16</v>
+        <v>2.22</v>
       </c>
       <c r="V3">
-        <v>0.06737739872068231</v>
+        <v>0.03633387888707038</v>
       </c>
       <c r="W3">
-        <v>0.03261538461538462</v>
+        <v>0.1004098360655738</v>
       </c>
       <c r="X3">
-        <v>0.02757358565869102</v>
+        <v>0.05436035006801698</v>
       </c>
       <c r="Y3">
-        <v>0.005041798956693599</v>
+        <v>0.0460494859975568</v>
       </c>
       <c r="Z3">
-        <v>0.42878369772872</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="AA3">
-        <v>0.002841303769857921</v>
+        <v>0.07995541869941322</v>
       </c>
       <c r="AB3">
-        <v>0.02784538127976801</v>
+        <v>0.05450490775238739</v>
       </c>
       <c r="AC3">
-        <v>-0.02500407750991009</v>
+        <v>0.02545051094702584</v>
       </c>
       <c r="AD3">
-        <v>1.7</v>
+        <v>1.13</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.7</v>
+        <v>1.13</v>
       </c>
       <c r="AG3">
-        <v>-1.46</v>
+        <v>-1.09</v>
       </c>
       <c r="AH3">
-        <v>0.03497942386831276</v>
+        <v>0.01815844448015426</v>
       </c>
       <c r="AI3">
-        <v>0.04815864022662888</v>
+        <v>0.03725684141114408</v>
       </c>
       <c r="AJ3">
-        <v>-0.03213028169014085</v>
+        <v>-0.01816363939343443</v>
       </c>
       <c r="AK3">
-        <v>-0.04542626011200996</v>
+        <v>-0.03877623621487016</v>
       </c>
       <c r="AL3">
-        <v>0.07099999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="AM3">
-        <v>-0.5760000000000001</v>
+        <v>-0.569</v>
       </c>
       <c r="AN3">
-        <v>2.230971128608924</v>
+        <v>0.4094202898550725</v>
       </c>
       <c r="AO3">
-        <v>1.112676056338028</v>
+        <v>32.42424242424242</v>
       </c>
       <c r="AP3">
-        <v>-1.916010498687664</v>
+        <v>-0.3949275362318842</v>
       </c>
       <c r="AQ3">
-        <v>-0.1371527777777778</v>
+        <v>-3.760984182776802</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/romania/romania_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_financial_svcs_non_bank_insurance.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0843</v>
+        <v>0.143</v>
       </c>
       <c r="E2">
-        <v>0.0407</v>
+        <v>0.0645</v>
       </c>
       <c r="G2">
-        <v>0.1261261261261261</v>
+        <v>0.1745222929936306</v>
       </c>
       <c r="H2">
-        <v>0.1261261261261261</v>
+        <v>0.1745222929936306</v>
       </c>
       <c r="I2">
-        <v>0.1927927927927928</v>
+        <v>0.2681528662420382</v>
       </c>
       <c r="J2">
-        <v>0.165241198645454</v>
+        <v>0.2305093114952987</v>
       </c>
       <c r="K2">
-        <v>2.45</v>
+        <v>4.4</v>
       </c>
       <c r="L2">
-        <v>0.2207207207207207</v>
+        <v>0.2802547770700637</v>
       </c>
       <c r="M2">
-        <v>1.743</v>
+        <v>2.2</v>
       </c>
       <c r="N2">
-        <v>0.02852700490998364</v>
+        <v>0.01877133105802048</v>
       </c>
       <c r="O2">
-        <v>0.7114285714285714</v>
+        <v>0.5</v>
       </c>
       <c r="P2">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="Q2">
-        <v>0.02504091653027823</v>
+        <v>0.01877133105802048</v>
       </c>
       <c r="R2">
-        <v>0.6244897959183673</v>
+        <v>0.5</v>
       </c>
       <c r="S2">
-        <v>0.2130000000000001</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.1222030981067126</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>2.22</v>
+        <v>4.94</v>
       </c>
       <c r="V2">
-        <v>0.03633387888707038</v>
+        <v>0.04215017064846417</v>
       </c>
       <c r="W2">
-        <v>0.1004098360655738</v>
+        <v>0.2046511627906977</v>
       </c>
       <c r="X2">
-        <v>0.05436035006801698</v>
+        <v>0.05789934595167011</v>
       </c>
       <c r="Y2">
-        <v>0.0460494859975568</v>
+        <v>0.1467518168390276</v>
       </c>
       <c r="Z2">
-        <v>0.4838709677419355</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="AA2">
-        <v>0.07995541869941322</v>
+        <v>0.1773148549963837</v>
       </c>
       <c r="AB2">
-        <v>0.05450490775238739</v>
+        <v>0.05790053776843545</v>
       </c>
       <c r="AC2">
-        <v>0.02545051094702584</v>
+        <v>0.1194143172279482</v>
       </c>
       <c r="AD2">
-        <v>1.13</v>
+        <v>2.86</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.13</v>
+        <v>2.86</v>
       </c>
       <c r="AG2">
-        <v>-1.09</v>
+        <v>-2.080000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.01815844448015426</v>
+        <v>0.02382142262202232</v>
       </c>
       <c r="AI2">
-        <v>0.03725684141114408</v>
+        <v>0.07322068612391193</v>
       </c>
       <c r="AJ2">
-        <v>-0.01816363939343443</v>
+        <v>-0.01806810284920084</v>
       </c>
       <c r="AK2">
-        <v>-0.03877623621487016</v>
+        <v>-0.06096131301289567</v>
       </c>
       <c r="AL2">
-        <v>0.066</v>
+        <v>0.057</v>
       </c>
       <c r="AM2">
-        <v>-0.569</v>
+        <v>-1.113</v>
       </c>
       <c r="AN2">
-        <v>0.4094202898550725</v>
+        <v>0.57429718875502</v>
       </c>
       <c r="AO2">
-        <v>32.42424242424242</v>
+        <v>73.85964912280701</v>
       </c>
       <c r="AP2">
-        <v>-0.3949275362318842</v>
+        <v>-0.4176706827309238</v>
       </c>
       <c r="AQ2">
-        <v>-3.760984182776802</v>
+        <v>-3.782569631626235</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0843</v>
+        <v>0.143</v>
       </c>
       <c r="E3">
-        <v>0.0407</v>
+        <v>0.0645</v>
       </c>
       <c r="G3">
-        <v>0.1261261261261261</v>
+        <v>0.1745222929936306</v>
       </c>
       <c r="H3">
-        <v>0.1261261261261261</v>
+        <v>0.1745222929936306</v>
       </c>
       <c r="I3">
-        <v>0.1927927927927928</v>
+        <v>0.2681528662420382</v>
       </c>
       <c r="J3">
-        <v>0.165241198645454</v>
+        <v>0.2305093114952987</v>
       </c>
       <c r="K3">
-        <v>2.45</v>
+        <v>4.4</v>
       </c>
       <c r="L3">
-        <v>0.2207207207207207</v>
+        <v>0.2802547770700637</v>
       </c>
       <c r="M3">
-        <v>1.743</v>
+        <v>2.2</v>
       </c>
       <c r="N3">
-        <v>0.02852700490998364</v>
+        <v>0.01877133105802048</v>
       </c>
       <c r="O3">
-        <v>0.7114285714285714</v>
+        <v>0.5</v>
       </c>
       <c r="P3">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="Q3">
-        <v>0.02504091653027823</v>
+        <v>0.01877133105802048</v>
       </c>
       <c r="R3">
-        <v>0.6244897959183673</v>
+        <v>0.5</v>
       </c>
       <c r="S3">
-        <v>0.2130000000000001</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.1222030981067126</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>2.22</v>
+        <v>4.94</v>
       </c>
       <c r="V3">
-        <v>0.03633387888707038</v>
+        <v>0.04215017064846417</v>
       </c>
       <c r="W3">
-        <v>0.1004098360655738</v>
+        <v>0.2046511627906977</v>
       </c>
       <c r="X3">
-        <v>0.05436035006801698</v>
+        <v>0.05789934595167011</v>
       </c>
       <c r="Y3">
-        <v>0.0460494859975568</v>
+        <v>0.1467518168390276</v>
       </c>
       <c r="Z3">
-        <v>0.4838709677419355</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="AA3">
-        <v>0.07995541869941322</v>
+        <v>0.1773148549963837</v>
       </c>
       <c r="AB3">
-        <v>0.05450490775238739</v>
+        <v>0.05790053776843545</v>
       </c>
       <c r="AC3">
-        <v>0.02545051094702584</v>
+        <v>0.1194143172279482</v>
       </c>
       <c r="AD3">
-        <v>1.13</v>
+        <v>2.86</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.13</v>
+        <v>2.86</v>
       </c>
       <c r="AG3">
-        <v>-1.09</v>
+        <v>-2.080000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.01815844448015426</v>
+        <v>0.02382142262202232</v>
       </c>
       <c r="AI3">
-        <v>0.03725684141114408</v>
+        <v>0.07322068612391193</v>
       </c>
       <c r="AJ3">
-        <v>-0.01816363939343443</v>
+        <v>-0.01806810284920084</v>
       </c>
       <c r="AK3">
-        <v>-0.03877623621487016</v>
+        <v>-0.06096131301289567</v>
       </c>
       <c r="AL3">
-        <v>0.066</v>
+        <v>0.057</v>
       </c>
       <c r="AM3">
-        <v>-0.569</v>
+        <v>-1.113</v>
       </c>
       <c r="AN3">
-        <v>0.4094202898550725</v>
+        <v>0.57429718875502</v>
       </c>
       <c r="AO3">
-        <v>32.42424242424242</v>
+        <v>73.85964912280701</v>
       </c>
       <c r="AP3">
-        <v>-0.3949275362318842</v>
+        <v>-0.4176706827309238</v>
       </c>
       <c r="AQ3">
-        <v>-3.760984182776802</v>
+        <v>-3.782569631626235</v>
       </c>
     </row>
   </sheetData>
